--- a/data/trans_dic/P41D_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,28</t>
+          <t>0,0; 67,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,42</t>
+          <t>0,0; 85,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,69</t>
+          <t>0,0; 70,56</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,41</t>
+          <t>0,0; 78,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,04</t>
+          <t>0,0; 54,64</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,62</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 60,85</t>
+          <t>9,28; 59,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 41,09</t>
+          <t>7,36; 41,91</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 747</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5307</t>
+          <t>0; 5591</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1265</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4496</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 818</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1368</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3094</t>
+          <t>0; 3058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 3812</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6071</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>986; 7024</t>
+          <t>1071; 6917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1816; 10213</t>
+          <t>1830; 10417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41D_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Habitat-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,96</t>
+          <t>0,0; 76,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,71</t>
+          <t>0,0; 60,09</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,91</t>
+          <t>0,0; 84,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,56</t>
+          <t>0,0; 72,97</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,5</t>
+          <t>0,0; 80,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,64</t>
+          <t>0,0; 47,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,08</t>
+          <t>0,0; 41,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 59,91</t>
+          <t>8,52; 61,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 41,91</t>
+          <t>6,77; 40,57</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5483</t>
+          <t>0; 5832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5591</t>
+          <t>0; 5398</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1750</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 3745</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4496</t>
+          <t>0; 4915</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2186</t>
+          <t>0; 2153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3286</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3058</t>
+          <t>0; 3192</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3812</t>
+          <t>0; 3361</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1071; 6917</t>
+          <t>1012; 7250</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1830; 10417</t>
+          <t>1765; 10568</t>
         </is>
       </c>
     </row>
